--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -1669,7 +1669,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Постановление адм. Псковской обл. № 206; распоряжение Красноярского края № 607-п; пост. Правительства Ленобласти № 458; пост. Правительства ХМАО № 306-п</t>
+          <t>Постановление адм. Псковской обл. № 206; постановление Правительства Красноярского края № 607-п; пост. Правительства Ленобласти № 458; пост. Правительства ХМАО № 306-п</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ФЗ № 442-ФЗ «Об основах социального обслуживания граждан в РФ», ст. 7, 14, 17, 31, 32</t>
+          <t>ФЗ № 442-ФЗ «Об основах социального обслуживания граждан в РФ», ст. 9, 16, 17, 31, 32</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>плата за стационар ≤75% среднедушевого дохода; ИППСУ; договор</t>
+          <t>Ст. 9 — права получателя соцуслуг; ст. 16 — ИППСУ; ст. 32 — плата за стационар ≤75% среднедушевого дохода; ст. 31 — порядок платы</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>СанПиН 2.3/2.4.3590-20 (пост. Гл. сан. врача РФ от 27.10.2020 № 32), п. 7.1.11–7.1.14, 8.4.1</t>
+          <t>СанПиН 2.3/2.4.3590-20 (пост. № 32 от 27.10.2020), п. 7.1.11–7.1.14, 8.4.1; с 01.09.2026 заменяется СанПиН 2.3/2.4.4282-26 (пост. № 18 от 02.06.2026), п. 56 подп. 11–14</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://base.garant.ru/74891586/</t>
+          <t>https://base.garant.ru/74891586/ ; 4282-26: https://base.garant.ru/414329257/</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>действует (с изм.)</t>
+          <t>3590-20 действует до 31.08.2026; 4282-26 вступает 01.09.2026 (пост. № 18 зарегистрировано Минюстом 02.06.2026 № 86854)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>прямая норма о питании в СОСО: не менее 3 раз/день, диетическое по показаниям; пробы, бракераж, питьевой режим</t>
+          <t>СОСО: питание ≥3 раз/день, диетическое по показаниям; суточные пробы; число вариантов блюд не ограничено</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>п. 7.1.11 — ключевая применимая норма к ПНИ/ДСО</t>
+          <t>Переход через 5 дней после семинара 25–27.08.2026. Для стационарного соцобслуживания норма «≥3 приёмов + диета» сохраняется (п. 56(11) 4282-26).</t>
         </is>
       </c>
     </row>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -465,1313 +465,1598 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Источник (наименование)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Тип/уровень</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Орган/автор</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Статус на дату проверки</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Что подтверждает</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Где используется</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Уровень уверенности</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>S001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>ФЗ № 442-ФЗ «Об основах социального обслуживания граждан в РФ», ст. 9, 16, 17, 31, 32</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>федеральный закон / A</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Госдума</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>https://www.consultant.ru/document/cons_doc_LAW_156558/</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>действует</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Ст. 9 — права получателя соцуслуг; ст. 16 — ИППСУ; ст. 32 — плата за стационар ≤75% среднедушевого дохода; ст. 31 — порядок платы</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>правовые главы</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>текст ст. 32 сверен по КонсультантПлюс (ред. 01.01.2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>S002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Приказ Минтруда России от 13.09.2022 № 520н «Об утверждении рекомендуемых норм питания...»</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>приказ / A</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Минтруд России</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>https://www.garant.ru/products/ipo/prime/doc/405607433/</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>действует</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>рекомендуемые суточные нормы питания для взрослых и детей в стационаре</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>глава о нормах питания</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>заменил приказ № 552н от 13.08.2014; статус — рекомендуемые</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>S003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>СанПиН 2.3/2.4.3590-20 (пост. № 32 от 27.10.2020), п. 7.1.11–7.1.14, 8.4.1; с 01.09.2026 заменяется СанПиН 2.3/2.4.4282-26 (пост. № 18 от 02.06.2026), п. 56 подп. 11–14</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>СанПиН 2.3/2.4.3590-20 (пост. ГГСВ РФ от 27.10.2020 № 32), п. 7.1.11–7.1.14 — до 01.09.2026; СанПиН 2.3/2.4.4282-26 (пост. ГГСВ РФ от 02.06.2026 № 18, зарег. в Минюсте 02.06.2026 № 86854), п. 56 подп. 11–14, п. 62, раздел VI</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>санитарные правила / A</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Роспотребнадзор</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>https://base.garant.ru/74891586/ ; 4282-26: https://base.garant.ru/414329257/</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://rovenkiadm.gosuslugi.ru/netcat_files/userfiles/SanPiN_2.4.4282-26.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>17.08.2026</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3590-20 действует до 31.08.2026; 4282-26 вступает 01.09.2026 (пост. № 18 зарегистрировано Минюстом 02.06.2026 № 86854)</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>СОСО: питание ≥3 раз/день, диетическое по показаниям; суточные пробы; число вариантов блюд не ограничено</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3590-20 действует до 01.09.2026; 4282-26 действует с 01.09.2026 до 01.09.2032</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>прямые нормы о питании в СОСО: не менее 3 раз/день, диетическое по показаниям (п. 56 подп. 11); суточные пробы при аутсорсинге (подп. 12), бракераж (подп. 13), привлекаемые предприятия (подп. 14); питьевой режим (п. 62); кейтеринг (раздел VI)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>санитарная глава</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Переход через 5 дней после семинара 25–27.08.2026. Для стационарного соцобслуживания норма «≥3 приёмов + диета» сохраняется (п. 56(11) 4282-26).</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>текст 4282-26 сверен по официальной публикации 17.08.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>S004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Исследование «Если быть точным»: «Как устроены ПНИ в России» (09.04.2026)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>исследование на госданных / D</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>ТАСС (проект)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>https://tochno.st/materials/kak-ustroeny-pni-v-rossii-issledovanie-esli-byt-tocnym</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>актуально (апрель 2026)</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>466 ПНИ (2024), 139 тыс. жителей, 65% старше 45, 74% недееспособных, 11% постельных, 289 мест, 41 регион переименовал в ДСО, 174 тыс. всего (Минтруд), 730+ организаций, СП 7000/1800</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>глава о системе</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>средняя (пересказ госданных; первичные ряды Минтруда в открытом виде не извлечены)</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>перепроверено по 3 независимым изданиям (АСИ, Ведомости, Forbes)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>S005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Ведомости: «Психоневрологических интернатов за три года стало на 13% меньше» (10.04.2026)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>СМИ / D</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Ведомости</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>https://www.vedomosti.ru/society/articles/2026/04/10/1189295-psihonevrologicheskih-internatov-stalo-menshe</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>актуально</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>подтверждение S004 + позиция Минтруда (174 тыс., 730 организаций) + кейс «Обручевский» (нояб. 2025)</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>глава о системе</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>S006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Приказ Минфина России от 30.03.2015 № 52н: статус на 2026 г.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>приказ / A (статус — по профильным изданиям)</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Минфин России</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>https://base.garant.ru/58070703/</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>действует; электронные формы вводятся постепенно (приказы 61н, 142н, 100н, 157н, 174н)</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>меню-требование ф. 0504202 остаётся в классе 05 ОКУД; бумажные формы допустимы для отдельных документов</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>учётная глава</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>прямой текст 52н открыт по обзору Гаранта; актуальные изменения 2025–2026 проверить дополнительно</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>S007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Страница семинара на сайте Минтруда: mintrud.gov.ru/events/1481</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>официальный сайт / A</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Минтруд России</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://mintrud.gov.ru/events/1481</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>существует (подтверждено поисковой выдачей, публикация 18.07.2026)</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>семинар «Пространство Новых Идей 2.0», СПб, 25–27.08.2026</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>введение</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>прямое открытие — тайм-аут; полный текст не извлечён, расхождений с письмом нет</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>S008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Постановление Правительства Красноярского края от 17.12.2014 № 607-п (нормы питания), актуальная ред.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>региональный НПА / A</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Правительство Красноярского края</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://ctonus.ru/f/normy_pitaniya.docx</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>действует (ред. с изм. по 2021)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>региональные нормы питания со ссылкой на 442-ФЗ, 520н-предшественник, СанПиН</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>региональная глава</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>текст извлечён с сайта учреждения; первоисточник — zakon.krskstate.ru (проверить)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>S009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Ст. 31 442-ФЗ + ПП РФ № 1075 (расчёт среднедушевого дохода)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>федеральный закон/ПП / A</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Правительство РФ</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>https://www.consultant.ru/law/podborki/plata_za_stacionarnoe_socialnoe_obsluzhivanie/</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>действует</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>правила платы и бесплатного предоставления</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>финансовая глава</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>S010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Письмо Минтруда о семинаре + список участников (приложения пользователя)</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>первичный документ / A</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Минтруд России</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>даты, место, тема, организаторы; 170 записей участников, 51 субъект</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>введение, глава об аудитории</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>список очищен: PARTICIPANTS_CLEAN.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>S011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Закон РФ № 3185-1 «О психиатрической помощи...», ст. 37, 39, 43, 44</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>закон / A</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>ВС РФ</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://www.consultant.ru/document/cons_doc_LAW_4205/</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>действует (ред. 04.08.2023, с изм. 01.09.2024)</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>ст. 43: проживающие в СОСО для лиц с ПР пользуются правами ст. 37; ежегодное освидетельствование комиссией с психиатром; перевод в организацию общего типа</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>правовые главы, дееспособность</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>ключевая норма для ПНИ/ДСО</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>S012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Прокуратура: проверки питания в соцучреждениях, дела по ст. 6.6 КоАП (Кашин СРЦ 2022; Зеленогорск 2021; представление 19.03.2024 soc13.ru)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>контрольная практика / B</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>прокуратуры районов</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>https://www.kashin.info/prokuratura-informiruet/novosti-prokuratury/9121</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>подтверждено</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>ст. 6.6 КоАП применяется к соцучреждениям за просрочку, отсутствие суточных проб; штраф 5 тыс. должн. лицу</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>глава о проверках, ответственности</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>высокая (для факта практики)</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>не ПНИ, но соцучреждения — ограниченная аналогия с маркировкой</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>S013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>ФАС: картель на торгах поставки соц. значимых продуктов, 543 торга, 4,7 млрд руб. (25.07.2024, РГ)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>антимонопольная практика / B</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ФАС России</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>https://rg.ru/2024/07/25/fas-raskryla-kartel-na-torgah-na-postavku-socialno-znachimyh-produktov.html</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>подтверждено</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>риски завышения цен на закупках продуктов для муниципальных учреждений</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>закупки</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Москва, МО, Владимирская обл., Дагестан</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>S014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>ФАС/ФСБ: картель на школьном питании Челябинск, 27 тендеров 2022–2024, штраф 5,1 млн (01.08.2025)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>антимонопольная практика / B</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>УФАС Челябинской обл.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>https://www.pro-goszakaz.ru/news/116068</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>подтверждено</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>схема мнимых заявок; уголовное дело по ст. 178 УК</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>закупки</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>школьное питание — ограниченная аналогия</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>S015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>ГАУССО НСО «Болотнинский ПНИ»: «Вариативное питание» (16.08.2024)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>практика учреждения / C</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Болотнинский ПНИ</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://bpni.nso.ru/news/2312</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>подтверждено (новость на офиц. сайте)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>с 2024 неск. раз/нед: завтрак — чай/какао/кофейный напиток, каша или суп; обед — салаты, вторые, десерт; перечень определяет диетсестра</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>региональные модели, кейсы</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>высокая (для факта сообщения)</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>участник семинара №118 (Тогучинский) и №117 (Успенский) — та же НСО</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>S016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>ГАУССО НСО «Успенский ПНИ»: вариативное меню во всех отделениях (13.08.2024)</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>практика учреждения / C</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Успенский ПНИ</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>https://upni.nso.ru/news/1916</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>подтверждено (новость на офиц. сайте)</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>ВСЕ отделения: выбор из двух вторых блюд, двух салатов, двух напитков; страхи персонала не подтвердились; обновлена посуда, занятия по этикету</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>региональные модели, кейсы</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>высокая (для факта сообщения)</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Успенский ПНИ — участник семинара №117</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>S017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>ОГБУСО «Усть-Илимский дом социального обслуживания»: «Что за зверь такой? Вариативное питание» (27.09.2024)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>практика учреждения / C</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Усть-Илимский ДСО</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>https://ui-ogbuso.ru/novosti/</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>подтверждено (новость на офиц. сайте)</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>с сентября 2024 поэтапное введение; предварительный опрос предпочтений, группировка блюд по популярности; старт — для посещающих столовую</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>региональные модели, кейсы</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>высокая (для факта сообщения)</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Усть-Илимский ДСО — участник семинара №94 (Иркутская обл.)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>S018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Иркутская область: вариативное питание в стационарных учреждениях — выбор из двух первых, вторых и гарниров (14.02.2025)</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>региональная практика / C</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>минсоцразвития ИО (пересказ bezformata)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>https://irkutsk.bezformata.com/listnews/variativnoe/142531226/</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>подтверждено (пресс-релиз)</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>выбор из 2 первых, 2 вторых, гарниров ежедневно — масштабирование на уровне региона</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>региональные модели</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>пересказ; первоисточник — сайт минсоцразвития ИО</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>S019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>ДДСОЛ (Московская обл.): 14-дневное вариативное меню, совет по питанию, замены по желанию жителей с врачом</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>практика учреждения / C</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>ДДСОЛ</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://ddsol.ru/about/pitanie/</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>подтверждено (страница офиц. сайта)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>зимнее/летнее 14-дневное меню, 5–6-разовое, совет по питанию (приказ 330н), замены по желанию + согласование с врачом; распоряжение Минсоцразвития МО 19РВ-32 от 13.04.2017</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>региональные модели, лечебное питание</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>высокая (для факта страницы)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>пример встраивания вариативности в действующую нормативную рамку</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>S020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Постановление Правительства Москвы № 1068-ПП (нормы питания в стационарных организациях)</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>региональный НПА / A</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Правительство Москвы</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>действовало на дату проверки 2025 (аудит Д1)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>московские нормы питания, таблицы замен</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>региональные модели</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>перенесено из реестра Д1; редакцию 2026 проверить</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>S021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Постановление адм. Псковской обл. № 206; постановление Правительства Красноярского края № 607-п; пост. Правительства Ленобласти № 458; пост. Правительства ХМАО № 306-п</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>региональные НПА / A</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>органы субъектов</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>действовали на дату проверки 2025 (аудит Д1); Красноярск 607-п перепроверен 23.07.2026</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>региональные нормы питания со ссылками на 442-ФЗ, приказ Минтруда, СанПиН</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>региональные модели</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>перенесено из реестра Д1 + перепроверка S008</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>S022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Постановление ВС РФ от 21.02.2019 № 11-АД19-4 (переквалификация 6.6→6.7 КоАП)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>судебная практика / A</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Верховный Суд РФ</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>https://www.garant.ru/products/ipo/prime/doc/72095418/</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>подтверждено</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>границы применения ст. 6.6/6.7 КоАП к учреждениям</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>ответственность</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>детское учреждение — ограниченная аналогия с маркировкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>S023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ФЗ от 05.04.2013 № 44-ФЗ «О контрактной системе в сфере закупок товаров, работ, услуг для обеспечения государственных и муниципальных нужд»</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>федеральный закон / A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Госдума</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_144624/</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>действует</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>контрактная система закупок; правовая рамка аутсорсинга питания</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>глава 44, раздел 30</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Лозовская С.О. «Правосубъектность лиц, признанных недееспособными и ограниченно дееспособными вследствие психического расстройства»</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>научная статья / B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Вестник Университета имени О.Е. Кутафина (МГЮА), 2023, № 5, с. 139–146</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://vestnik.msal.ru/jour/article/view/2058</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>опубликовано</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>практика применения п. 2 ст. 30 ГК: институт невостребован, критерии размыты</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>раздел 16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>DOI 10.17803/2311-5998.2023.105.5.139-146</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>S025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>«Кейтеринг в организациях социального обслуживания» (отраслевое издание, 2022)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>отраслевая статья / C</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Профиздат</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.profiz.ru/sec/4_2022/Kejtering/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>опубликовано</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>практика передачи питания на аутсорсинг в СОСО; вариативность через контракт</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>глава 44</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>S026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>«Услуга приготовления диетических блюд» — справочные материалы по организации лечебного питания</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>отраслевой материал / C</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Национальная ассоциация клинического питания (НАКП)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://nakp.org/usluga-prigotovleniya-dieticheskikh-blyud/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>опубликовано</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>опыт привлечённых предприятий для диетического питания</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>глава 44</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>СП 2.4.3648-20 «Санитарно-эпидемиологические требования к организациям воспитания и обучения, отдыха и оздоровления детей и молодежи» (пост. ГГСВ РФ от 28.09.2020 № 28, зарег. в Минюсте 18.12.2020 № 61573)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>санитарные правила / A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Роспотребнадзор</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_371594/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>действует (ред. от 24.12.2025)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>общие санитарные требования к детским организациям</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>приложение 41</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1949,27 +1949,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S026</t>
+          <t>S027</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>«Услуга приготовления диетических блюд» — справочные материалы по организации лечебного питания</t>
+          <t>СП 2.4.3648-20 «Санитарно-эпидемиологические требования к организациям воспитания и обучения, отдыха и оздоровления детей и молодежи» (пост. ГГСВ РФ от 28.09.2020 № 28, зарег. в Минюсте 18.12.2020 № 61573)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>отраслевой материал / C</t>
+          <t>санитарные правила / A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Национальная ассоциация клинического питания (НАКП)</t>
+          <t>Роспотребнадзор</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://nakp.org/usluga-prigotovleniya-dieticheskikh-blyud/</t>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_371594/</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1979,82 +1979,25 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>опубликовано</t>
+          <t>действует (ред. от 24.12.2025)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>опыт привлечённых предприятий для диетического питания</t>
+          <t>общие санитарные требования к детским организациям</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>глава 44</t>
+          <t>приложение 41</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>S027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>СП 2.4.3648-20 «Санитарно-эпидемиологические требования к организациям воспитания и обучения, отдыха и оздоровления детей и молодежи» (пост. ГГСВ РФ от 28.09.2020 № 28, зарег. в Минюсте 18.12.2020 № 61573)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>санитарные правила / A</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Роспотребнадзор</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>https://www.consultant.ru/document/cons_doc_LAW_371594/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>действует (ред. от 24.12.2025)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>общие санитарные требования к детским организациям</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>приложение 41</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2003,6 +2003,80 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>S028</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Письмо Минтруда России от 21.04.2020 № 26-4/10/В-3076: методические рекомендации по организации работы стационарных организаций социального обслуживания в условиях COVID-19 (усиленный питьевой режим, раздача в жилые комнаты, дезинфекционный контур)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>письмо / A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Минтруд России</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://normativ.kontur.ru/document?moduleId=8&amp;documentId=361442</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>проверено 18.08.2026 по тексту письма</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>глава 18.11 (карантин)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S029</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Методические рекомендации по организации питания в учреждениях (отделениях) социального обслуживания граждан пожилого возраста и инвалидов (пост. Минтруда России от 15.02.2002 № 12, ред. приказа от 04.06.2007 № 397): лечебно-профилактические продукты, профилактика витаминной недостаточности, санитарная безопасность</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>методические рекомендации / A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Минтруд России</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://docs.cntd.ru/document/901816611</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>проверено 18.08.2026 по тексту</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>глава 18.11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2077,6 +2077,63 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S030</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Комитет по социальной политике Санкт-Петербурга: «Работа по развитию психоневрологических интернатов продолжается» (22.07.2025) — первые результаты вариативного меню в ДСО «Серафимовский»</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>практика учреждения / C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Комитет по социальной политике СПб / ДСО «Серафимовский»</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.gov.spb.ru/gov/otrasl/trud/news/302216/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>17.08.2026</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>подтверждено (официальный сайт Администрации СПб)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>несколько месяцев: выбор рациона накануне для части жителей; закупка оборудования и доп. сотрудники; энтузиазм жителей; полный переход крайне затруднителен (нормы, здоровье; выбор популярного, не самого полезного)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>гл. 25 (кейс 4), 2, 4, 17, 23, 41; слайды 13, 16; речь</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>высокая (для факта сообщения)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>новость учредителя, не аудит; докладчик семинара — директор дома; опровергает универсальный вывод «все начинали без новых денег»</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2134,6 +2134,177 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S031</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Письмо Комитета по социальной политике Санкт-Петербурга руководителям государственных учреждений об усилении контроля за исполнением поставщиками питания своих обязательств (ст. 34, 94, 95 44-ФЗ; ежедневный мониторинг, акты, претензии, одностороннее расторжение, РНП)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>разъяснение учредителя / A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Комитет по социальной политике Санкт-Петербурга (председатель Е.Н. Фидрикова)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>— (внутренний документ Комитета; оригинал у автора, PDF)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>действует</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Обязанность заказчика контролировать соответствие продуктов и услуг условиям контракта (ст. 34, 94 44-ФЗ); процедура: ежедневный мониторинг веса порций и температур, акты, требования об устранении со сроком, претензионная работа, расторжение по ст. 95 + РНП; судебная практика требует строгой фиксации нарушений</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>раздел 17.12 доклада (вопрос 6), раздел 42</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Номер и дата письма в тексте не указаны — уточнить у автора</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>S032</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 05.08.2003 № 330н «О мерах по совершенствованию лечебного питания в лечебно-профилактических учреждениях РФ» (Инструкция по организации лечебного питания, диеты по Певзнеру; действующая редакция — с изм., внесёнными приказом Минздрава России от 19.02.2024 № 70н)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>приказ / A</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Минздрав России (рег. Минюст 12.09.2003 № 5073)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_44323/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>действует</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Инструкция по организации лечебного питания адресована лечебно-профилактическим учреждениям (ЛПУ); диеты по Певзнеру как основа диетстолов; на организации социального обслуживания не распространяется автоматически</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>раздел 17.12 доклада (вопросы 3–4), раздел 17.5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Реквизиты подтверждены по КонсультантПлюс/Гарант/СудАкт; изменения 70н от 19.02.2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>S033</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 21.06.2013 № 395н «Об утверждении норм лечебного питания» (действующая редакция — с изм., внесёнными приказом Минздрава России от 19.02.2024 № 70н)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>приказ / A</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Минздрав России (рег. Минюст 05.07.2013 № 28995)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.consultant.ru/document/cons_doc_LAW_149196/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>действует</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Нормы лечебного питания (среднесуточные наборы продуктов для диет); адресованы медицинским организациям; на СОСО не распространяются автоматически</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>раздел 17.12 доклада (вопросы 3–4), раздел 17.5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Внимание: в ряде публикаций приказу 395н ошибочно приписывают дату 23.09.2020 — верная дата 21.06.2013</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2305,6 +2305,48 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>S034</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Извещение № 0372200070825000244: открытый конкурс в электронной форме «Поставка продуктов питания» СПб ГБСУСОН «ДСО «Тесовый берег» (ИНН 7827661874); обеспечение заявки по ст. 45 44-ФЗ; опубликовано 24.11.2025, площадка АГЗ РТ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>закупка / B</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>СПб ГБСУСОН «ДСО «Тесовый берег»</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.tenderguru.ru/tender/90473908</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>подтверждено вторичным агрегатором (tenderguru); номер извещения и ссылка на ст. 45 44-ФЗ в тексте извещения</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ОПФ бюджетного учреждения и режим 44-ФЗ (в отличие от автономного Серафимовского по 223-ФЗ)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2347,6 +2347,28 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>S035</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Приказ директора СПб ГАСУСОН «ДСО «Серафимовский» от 10.03.2026 № 124 «Об организации зала заказного питания» (вариативное меню; опубликован на официальном сайте учреждения www.pni9.ru)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>локальный акт / B</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>СПб ГАСУСОН «ДСО «Серафимовский» (www.pni9.ru)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -2355,7 +2355,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Приказ директора СПб ГАСУСОН «ДСО «Серафимовский» от 10.03.2026 № 124 «Об организации зала заказного питания» (вариативное меню; опубликован на официальном сайте учреждения www.pni9.ru)</t>
+          <t>Приказ директора СПб ГАСУСОН «ДСО «Серафимовский» от 10.03.2026 № 124 «Об утверждении правил внутреннего распорядка жителей СПб ГАСУСОН «ДСО «Серафимовский»» (в правилах закреплено заказное питание — вариативное меню, в т. ч. для маломобильных граждан; PDF опубликован на www.pni9.ru)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр источников" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Реестр источников" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр источников'!$A$1:$K$11</definedName>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -520,6 +520,11 @@
           <t>Примечание</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Доступность первоисточника</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -577,6 +582,11 @@
           <t>текст ст. 32 сверен по КонсультантПлюс (ред. 01.01.2026)</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -634,6 +644,11 @@
           <t>заменил приказ № 552н от 13.08.2014; статус — рекомендуемые</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -691,6 +706,11 @@
           <t>текст 4282-26 сверен по официальной публикации 17.08.2026</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -710,7 +730,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ТАСС (проект)</t>
+          <t>проект «Если быть точным»</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -725,7 +745,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>актуально (апрель 2026)</t>
+          <t>данные за 2024 год; публикация 09.04.2026 (не исследование ТАСС)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -746,6 +766,11 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>перепроверено по 3 независимым изданиям (АСИ, Ведомости, Forbes)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>вторичная публикация</t>
         </is>
       </c>
     </row>
@@ -805,6 +830,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>вторичная публикация</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -862,6 +892,11 @@
           <t>прямой текст 52н открыт по обзору Гаранта; актуальные изменения 2025–2026 проверить дополнительно</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>требует перепроверки</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -919,6 +954,11 @@
           <t>прямое открытие — тайм-аут; полный текст не извлечён, расхождений с письмом нет</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -976,6 +1016,11 @@
           <t>текст извлечён с сайта учреждения; первоисточник — zakon.krskstate.ru (проверить)</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>требует перепроверки</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1033,6 +1078,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1090,6 +1140,11 @@
           <t>список очищен: PARTICIPANTS_CLEAN.xlsx</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>внутренний документ</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1147,6 +1202,11 @@
           <t>ключевая норма для ПНИ/ДСО</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1204,6 +1264,11 @@
           <t>не ПНИ, но соцучреждения — ограниченная аналогия с маркировкой</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1261,6 +1326,11 @@
           <t>Москва, МО, Владимирская обл., Дагестан</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1318,6 +1388,11 @@
           <t>школьное питание — ограниченная аналогия</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1375,6 +1450,11 @@
           <t>участник семинара №118 (Тогучинский) и №117 (Успенский) — та же НСО</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1432,6 +1512,11 @@
           <t>Успенский ПНИ — участник семинара №117</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1489,6 +1574,11 @@
           <t>Усть-Илимский ДСО — участник семинара №94 (Иркутская обл.)</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1546,6 +1636,11 @@
           <t>пересказ; первоисточник — сайт минсоцразвития ИО</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>вторичная публикация</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1603,6 +1698,11 @@
           <t>пример встраивания вариативности в действующую нормативную рамку</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1660,6 +1760,11 @@
           <t>перенесено из реестра Д1; редакцию 2026 проверить</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>требует перепроверки</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1717,6 +1822,11 @@
           <t>перенесено из реестра Д1 + перепроверка S008</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>внутренний документ</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1774,6 +1884,11 @@
           <t>детское учреждение — ограниченная аналогия с маркировкой</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1831,6 +1946,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1888,6 +2008,11 @@
           <t>DOI 10.17803/2311-5998.2023.105.5.139-146</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1945,6 +2070,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2002,6 +2132,11 @@
           <t>—</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2039,6 +2174,11 @@
           <t>глава 18.11 (карантин)</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2076,6 +2216,11 @@
           <t>глава 18.11</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2133,6 +2278,11 @@
           <t>новость учредителя, не аудит; докладчик семинара — директор дома; опровергает универсальный вывод «все начинали без новых денег»</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2190,6 +2340,11 @@
           <t>Номер и дата письма в тексте не указаны — уточнить у автора</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>внутренний документ</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2247,6 +2402,11 @@
           <t>Реквизиты подтверждены по КонсультантПлюс/Гарант/СудАкт; изменения 70н от 19.02.2024</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2304,6 +2464,11 @@
           <t>Внимание: в ряде публикаций приказу 395н ошибочно приписывают дату 23.09.2020 — верная дата 21.06.2013</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>публичный первоисточник</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2346,6 +2511,11 @@
           <t>ОПФ бюджетного учреждения и режим 44-ФЗ (в отличие от автономного Серафимовского по 223-ФЗ)</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>вторичная публикация</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2366,6 +2536,11 @@
       <c r="D35" t="inlineStr">
         <is>
           <t>СПб ГАСУСОН «ДСО «Серафимовский» (www.pni9.ru)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>внутренний документ</t>
         </is>
       </c>
     </row>

--- a/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
+++ b/04_приложения_и_реестры/SOURCE_REGISTRY.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Реестр источников" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Реестр источников" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр источников'!$A$1:$K$11</definedName>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Приказ директора СПб ГАСУСОН «ДСО «Серафимовский» от 10.03.2026 № 124 «Об утверждении правил внутреннего распорядка жителей СПб ГАСУСОН «ДСО «Серафимовский»» (в правилах закреплено заказное питание — вариативное меню, в т. ч. для маломобильных граждан; PDF опубликован на www.pni9.ru)</t>
+          <t>Приказ директора СПб ГАСУСОН «ДСО «Серафимовский» от 10.03.2026 № 124 «Об утверждении правил внутреннего распорядка жителей СПб ГАСУСОН «ДСО «Серафимовский»» (в правилах закреплено заказное питание — вариативное меню, в т. ч. для маломобильных граждан; PDF опубликован на архив сайта: web.archive.org/web/20260415001233/https://www.pni9.ru/правила-внутреннего-распорядка/)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>СПб ГАСУСОН «ДСО «Серафимовский» (www.pni9.ru)</t>
+          <t>СПб ГАСУСОН «ДСО «Серафимовский» (архив сайта: web.archive.org/web/20260415001233/https://www.pni9.ru/правила-внутреннего-распорядка/)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
